--- a/backend/tests/services/rule_engine/fixtures/sample_matrix.xlsx
+++ b/backend/tests/services/rule_engine/fixtures/sample_matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,120 +424,240 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>PL Write Off</t>
+          <t>PL Write off</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Home Loan WO</t>
+          <t>Home Loan Write off</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Consumer Loan WO</t>
+          <t>Consumer Loan  Write off</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Agri Loan WO</t>
+          <t>Agri Loan  Write off</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>MSME Loan WO</t>
+          <t>MSME Loan  Write off</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Auto Loan WO</t>
+          <t>Auto Loan  Write off</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>CC Write Off</t>
+          <t>Credit Card Write Off</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>WO Amount</t>
+          <t>Write Off Amount</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Loan enquiry</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Existing A/C</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Existing A/C Holder</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Existing Car Loan</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Rented House-Salaried</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Rented House-Self Employed</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Unmarried</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>NRI/PIO</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Total Exp</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Current Exp</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Salary Mode</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Existing Car Loan</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Rented House SE</t>
-        </is>
-      </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>Minimium Stay Period for NRI</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Salaried</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Employment-Firm</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Employment-Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Employment-Public Ltd</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Employment-Govt</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Employment-PSU</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Minimum work experience</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Work Experience in current company</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Salary payment mode-Cash</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Salary payment mode- Bank Credit</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>No Income Proof</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Rental Income Non-ITR</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Rental Income Not Reflecting</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Rental Income-NON ITR</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Rental Income-ITR</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Rental Income-Not reflecting in Bank</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Rental Income-reflecting in Bank</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Minimum Salary</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Min Bus Income</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Self Employed</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Self employed ITR Filled</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ITR Not Filed</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Business Proof</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Propreitorship</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Parternship Firm</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Private Limited</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Public Limited</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Currently Outstanding</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>EMI/Income</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Bank Name</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -579,86 +699,136 @@
           <t>false</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>&lt; 5000</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>[21..70]</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>&gt;= 2</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>&gt;= 1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>"Bank Credit"</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>&gt;= 25000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>"BOI"</t>
-        </is>
-      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>&gt;= 100000</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>"Mandatory"</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>BOI</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -701,76 +871,123 @@
           <t>false</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>[18..70]</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>&gt;= 2</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>&gt;= 1</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>"Bank Credit"</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>&gt;= 25000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>"Indian Bank"</t>
-        </is>
-      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>&gt;= 100000</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>"Mandatory"</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Indian Bank</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -813,71 +1030,918 @@
           <t>false</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>&lt; 5000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>[21..70]</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>&gt;= 2</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>&gt;= 1</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>"Bank Credit"</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>&gt;= 25000</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>"IOB"</t>
-        </is>
-      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>&gt;= 100000</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>"Mandatory"</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>IOB</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>&gt;= 701</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>[21..70]</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>&gt;= 1</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>&gt;= 25000</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>&gt;= 100000</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>"Mandatory"</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>BOB</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>&gt;= 701</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>[21..60]</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>&gt;= 1</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>&gt;= 25000</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>&gt;= 100000</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>"Mandatory"</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>HDFC</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>&gt;= 701</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>[21..60]</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>&gt;= 1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>&gt;= 25000</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>&gt;= 100000</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>"Mandatory"</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>AXIS</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>&gt;= 701</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>[21..60]</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>&gt;= 1</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>&gt;= 25000</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>&gt;= 100000</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>"Mandatory"</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>Kotak</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>&gt;= 650</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>&lt; 5000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>[21..60]</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>&gt;= 1</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>&gt;= 25000</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>&gt;= 100000</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>"Mandatory"</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>BOM</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
